--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484777_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484777_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.813499999999999</v>
+        <v>7.1856</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0433</v>
+        <v>5.248</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7702</v>
+        <v>1.9376</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5422</v>
+        <v>2.7739</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3539</v>
+        <v>0.6723</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.8117</v>
+        <v>2.1016</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0346</v>
+        <v>5.0227</v>
       </c>
       <c r="K2" t="n">
-        <v>7.3963</v>
+        <v>1.1465</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3617</v>
+        <v>3.8762</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4925</v>
+        <v>-2.2488</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0424</v>
+        <v>-0.4742</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4501</v>
+        <v>-1.7746</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8305</v>
+        <v>3.5853</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2525</v>
+        <v>0.5438</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7827</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4698</v>
+        <v>-0.0404</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9624</v>
+        <v>2.1696</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.528</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9624</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3403</v>
+        <v>6.8557</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7994</v>
+        <v>4.9585</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5408</v>
+        <v>1.8972</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7739</v>
+        <v>4.5422</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6723</v>
+        <v>6.3539</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1016</v>
+        <v>-1.8117</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0227</v>
+        <v>7.0346</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1465</v>
+        <v>7.3963</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8762</v>
+        <v>-0.3617</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2488</v>
+        <v>-2.4925</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4742</v>
+        <v>-1.0424</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7746</v>
+        <v>-1.4501</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6983</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5853</v>
+        <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3016</v>
+        <v>2.2947</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1357</v>
+        <v>1.6979</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4373</v>
+        <v>0.5968</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1696</v>
+        <v>0.9624</v>
       </c>
       <c r="W3" t="n">
-        <v>1.528</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7674</v>
+        <v>3.7644</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3306</v>
+        <v>3.1689</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4368</v>
+        <v>0.5955</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0982</v>
@@ -766,13 +766,13 @@
         <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3797</v>
+        <v>0.6173</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1147</v>
+        <v>0.7236</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.265</v>
+        <v>-0.1063</v>
       </c>
       <c r="V4" t="n">
         <v>1.547</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4111</v>
+        <v>0.1063</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5616</v>
+        <v>0.8317</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9727</v>
+        <v>-0.7254</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2576</v>
+        <v>2.6811</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.223</v>
+        <v>1.7436</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0346</v>
+        <v>0.9375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6792</v>
+        <v>5.0054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0211</v>
+        <v>2.3149</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6581</v>
+        <v>2.6905</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9369</v>
+        <v>-2.3243</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2442</v>
+        <v>-0.5713</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6927</v>
+        <v>-1.753</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.661</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.8305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1534</v>
+        <v>0.2747</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1176</v>
+        <v>0.2611</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0359</v>
+        <v>0.0136</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7113</v>
+        <v>-0.3582</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2232</v>
+        <v>0.5616</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4881</v>
+        <v>-0.9198</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0977</v>
+        <v>-0.2576</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0697</v>
+        <v>-0.223</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0281</v>
+        <v>-0.0346</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0708</v>
+        <v>0.6792</v>
       </c>
       <c r="K8" t="n">
         <v>0.0211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0496</v>
+        <v>0.6581</v>
       </c>
       <c r="M8" t="n">
-        <v>0.027</v>
+        <v>-0.9369</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0485</v>
+        <v>-0.2442</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0216</v>
+        <v>-0.6927</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0588</v>
+        <v>-0.1005</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2939</v>
+        <v>-0.1176</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3527</v>
+        <v>0.0171</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1218</v>
+        <v>-0.6138</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1257</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4731</v>
+        <v>-0.4881</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5041</v>
+        <v>0.0977</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9391</v>
+        <v>0.0697</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5649</v>
+        <v>0.0281</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0912</v>
+        <v>0.0708</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2146</v>
+        <v>0.0211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1234</v>
+        <v>0.0496</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4128</v>
+        <v>0.027</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2755</v>
+        <v>0.0485</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6883</v>
+        <v>-0.0216</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8917</v>
+        <v>0.1562</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7824</v>
+        <v>-0.1965</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1094</v>
+        <v>0.3527</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1565</v>
+        <v>-0.703</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2989</v>
+        <v>0.1268</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8576</v>
+        <v>-0.8298</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6811</v>
+        <v>-0.7079</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7436</v>
+        <v>0.1057</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9375</v>
+        <v>-0.8136</v>
       </c>
       <c r="J10" t="n">
-        <v>5.0054</v>
+        <v>2.1733</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3149</v>
+        <v>0.6926</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6905</v>
+        <v>1.4807</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3243</v>
+        <v>-2.8812</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5713</v>
+        <v>-0.5869</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.753</v>
+        <v>-2.2942</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-2.8305</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-5.661</v>
-      </c>
       <c r="R10" t="n">
-        <v>2.8305</v>
+        <v>2.6418</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9881</v>
+        <v>0.4765</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8695000000000001</v>
+        <v>0.4823</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1187</v>
+        <v>-0.0058</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.019</v>
+        <v>-0.2828</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2262</v>
+        <v>0.3018</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>-0.5846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3934</v>
+        <v>-1.9277</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4578</v>
+        <v>-1.4282</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9356</v>
+        <v>-0.4995</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7079</v>
+        <v>-2.5041</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1057</v>
+        <v>-0.9391</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8136</v>
+        <v>-1.5649</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1733</v>
+        <v>-1.0912</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6926</v>
+        <v>-1.2146</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4807</v>
+        <v>0.1234</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8812</v>
+        <v>-1.4128</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5869</v>
+        <v>0.2755</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2942</v>
+        <v>-1.6883</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.214</v>
+        <v>0.0858</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1023</v>
+        <v>0.0029</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1116</v>
+        <v>0.0829</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2828</v>
+        <v>0.3018</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5846</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1401</v>
+        <v>-3.0285</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2126</v>
+        <v>-1.1538</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9276</v>
+        <v>-1.8747</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4985</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2833</v>
+        <v>-0.1716</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2199</v>
+        <v>-0.1611</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0634</v>
+        <v>-0.0105</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.4887</v>
+        <v>13.7825</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3954</v>
+        <v>14.6895</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9069000000000003</v>
+        <v>-0.9070000000000005</v>
       </c>
       <c r="G13" t="n">
         <v>5.5303</v>
       </c>
       <c r="H13" t="n">
-        <v>9.751300000000002</v>
+        <v>9.751300000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-4.2208</v>
       </c>
       <c r="J13" t="n">
-        <v>21.94390000000001</v>
+        <v>21.9439</v>
       </c>
       <c r="K13" t="n">
         <v>13.1788</v>
@@ -1459,7 +1459,7 @@
         <v>-12.9859</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9435000000000003</v>
+        <v>0.9435000000000004</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.983</v>
@@ -1468,16 +1468,16 @@
         <v>17.9265</v>
       </c>
       <c r="S13" t="n">
-        <v>3.882900000000001</v>
+        <v>4.1769</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9829</v>
+        <v>3.2768</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.9001</v>
       </c>
       <c r="V13" t="n">
-        <v>3.132</v>
+        <v>3.132000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>6.4518</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5429</v>
+        <v>4.0468</v>
       </c>
       <c r="E14" t="n">
-        <v>4.84</v>
+        <v>5.1323</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2971</v>
+        <v>-1.0855</v>
       </c>
       <c r="G14" t="n">
         <v>4.4108</v>
@@ -1546,13 +1546,13 @@
         <v>2.6418</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2604</v>
+        <v>-0.7564</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6191</v>
+        <v>-0.3268</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6413</v>
+        <v>-0.4296</v>
       </c>
       <c r="V14" t="n">
         <v>0.5812</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4726</v>
+        <v>1.3042</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9901</v>
+        <v>2.7952</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5174</v>
+        <v>-1.491</v>
       </c>
       <c r="G15" t="n">
         <v>-1.7522</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3939</v>
+        <v>-0.5623</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3498</v>
+        <v>-0.5447</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.044</v>
+        <v>-0.0176</v>
       </c>
       <c r="V15" t="n">
         <v>3.0526</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7738</v>
+        <v>0.0533</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7285</v>
+        <v>1.8516</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9546</v>
+        <v>-1.7983</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0415</v>
@@ -1702,13 +1702,13 @@
         <v>3.0192</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4226</v>
+        <v>-0.2979</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2831</v>
+        <v>0.4062</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8605</v>
+        <v>-0.7042</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6830000000000001</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8103</v>
+        <v>-0.7128</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1764</v>
+        <v>-0.0789</v>
       </c>
       <c r="F17" t="n">
         <v>-0.6339</v>
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4362</v>
+        <v>-0.3388</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1764</v>
+        <v>-0.0789</v>
       </c>
       <c r="U17" t="n">
         <v>-0.2598</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0414</v>
+        <v>-0.8405</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3809</v>
+        <v>-1.2835</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3394</v>
+        <v>0.4429</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4012</v>
@@ -1858,13 +1858,13 @@
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0176</v>
+        <v>0.1833</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.164</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1464</v>
+        <v>0.2498</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2218</v>
+        <v>-1.4446</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2651</v>
+        <v>0.0041</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4869</v>
+        <v>-1.4488</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5272</v>
+        <v>-1.1197</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4429</v>
+        <v>-0.5243</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0843</v>
+        <v>-0.5954</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1761</v>
+        <v>0.2672</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3946</v>
+        <v>0.1268</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7815</v>
+        <v>0.1404</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7032</v>
+        <v>-1.3869</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8375</v>
+        <v>-0.6511</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8657</v>
+        <v>-0.7358</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0036</v>
+        <v>-0.0232</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2631</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6502</v>
+        <v>0.2399</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3208</v>
+        <v>-1.2452</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6957</v>
+        <v>-1.4767</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2184</v>
+        <v>-1.9366</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8773</v>
+        <v>-0.5272</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8103</v>
+        <v>-0.4429</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9329</v>
+        <v>-0.0843</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2453</v>
+        <v>2.1761</v>
       </c>
       <c r="K20" t="n">
-        <v>4.0311</v>
+        <v>1.3946</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2142</v>
+        <v>0.7815</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3679</v>
+        <v>-2.7032</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2208</v>
+        <v>-1.8375</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1471</v>
+        <v>-0.8657</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5096</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.2513</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0328</v>
+        <v>-0.4518</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2057</v>
+        <v>0.2005</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8905</v>
+        <v>-0.3208</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.9813</v>
+        <v>-0.3208</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.034</v>
+        <v>-2.4919</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1908</v>
+        <v>-0.0619</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8432</v>
+        <v>-2.43</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1197</v>
+        <v>1.8773</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5243</v>
+        <v>2.8103</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5954</v>
+        <v>-0.9329</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2672</v>
+        <v>4.2453</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1268</v>
+        <v>4.0311</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1404</v>
+        <v>0.2142</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3869</v>
+        <v>-2.3679</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6511</v>
+        <v>-1.2208</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7358</v>
+        <v>-1.1471</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9435</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6125</v>
+        <v>0.0308</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.458</v>
+        <v>0.4482</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1546</v>
+        <v>-0.4173</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2452</v>
+        <v>-2.8905</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.9813</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>-1.9092</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>A. CABALLERO ROMERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9892</v>
+        <v>-2.8097</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3579</v>
+        <v>-1.8559</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6313</v>
+        <v>-0.9538</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1725</v>
+        <v>-2.4832</v>
       </c>
       <c r="H22" t="n">
-        <v>0.882</v>
+        <v>-1.483</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0545</v>
+        <v>-1.0002</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7513</v>
+        <v>-1.6919</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3298</v>
+        <v>-1.1246</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5785</v>
+        <v>-0.5673</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9238</v>
+        <v>-0.7913</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4478</v>
+        <v>-0.3584</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.476</v>
+        <v>-0.4329</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
         <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0053</v>
+        <v>-0.0813</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2787</v>
+        <v>0.4777</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2734</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CABALLERO ROMERO</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0394</v>
+        <v>-3.1781</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9533</v>
+        <v>-2.6502</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0861</v>
+        <v>-0.5278</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4832</v>
+        <v>-1.1725</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.483</v>
+        <v>0.882</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0002</v>
+        <v>-2.0545</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6919</v>
+        <v>0.7513</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1246</v>
+        <v>2.3298</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5673</v>
+        <v>-1.5785</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7913</v>
+        <v>-1.9238</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3584</v>
+        <v>-1.4478</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4329</v>
+        <v>-0.476</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3774</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R23" t="n">
         <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.311</v>
+        <v>-0.1941</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3803</v>
+        <v>-0.571</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6913</v>
+        <v>0.3769</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9244</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4462</v>
+        <v>-5.2891</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3802</v>
+        <v>-3.4059</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.066</v>
+        <v>-1.8832</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9468</v>
@@ -2326,13 +2326,13 @@
         <v>3.0192</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0992</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9036</v>
+        <v>0.0708</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1956</v>
+        <v>-1.0128</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7019</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.4887</v>
+        <v>-12.8391</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9068999999999985</v>
+        <v>0.9069000000000011</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.3955</v>
+        <v>-13.746</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5303</v>
@@ -2395,7 +2395,7 @@
         <v>-8.7652</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9435</v>
+        <v>-0.9434999999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.9265</v>
@@ -2404,13 +2404,13 @@
         <v>16.983</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8828</v>
+        <v>-3.2332</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9001</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.9828</v>
+        <v>-2.3332</v>
       </c>
       <c r="V25" t="n">
         <v>-3.132000000000001</v>
